--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-07T12:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:05:50+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:13+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,6 +293,9 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -376,7 +379,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -434,6 +437,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -474,7 +481,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -554,7 +561,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -590,7 +597,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -696,72 +703,72 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -789,7 +796,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
 </t>
   </si>
   <si>
@@ -830,7 +837,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -888,7 +895,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -932,7 +939,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -985,7 +992,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1147,10 +1154,10 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1270,7 +1277,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1436,7 +1443,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1458,7 +1465,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1473,10 +1480,14 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1516,7 +1527,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2149,7 +2160,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2157,10 +2168,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2171,7 +2182,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>82</v>
@@ -2180,19 +2191,19 @@
         <v>82</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2242,13 +2253,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2277,10 +2288,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2291,7 +2302,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>82</v>
@@ -2300,16 +2311,16 @@
         <v>82</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2360,19 +2371,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2395,10 +2406,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2409,28 +2420,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2480,19 +2491,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2515,10 +2526,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2529,7 +2540,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2541,16 +2552,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2576,13 +2587,13 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>82</v>
@@ -2600,19 +2611,19 @@
         <v>82</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2635,21 +2646,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2661,16 +2672,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2720,19 +2731,19 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
@@ -2744,7 +2755,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2755,14 +2766,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2781,16 +2792,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2840,7 +2851,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2852,7 +2863,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2864,7 +2875,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2875,14 +2886,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2901,16 +2912,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2960,7 +2971,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2972,7 +2983,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2984,7 +2995,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -2995,14 +3006,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3015,25 +3026,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3082,7 +3093,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3094,7 +3105,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3106,7 +3117,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3117,10 +3128,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3140,20 +3151,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3202,7 +3213,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3214,22 +3225,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3237,14 +3248,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3260,20 +3271,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3322,7 +3333,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3334,19 +3345,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3357,14 +3368,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3380,19 +3391,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3442,7 +3453,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3454,19 +3465,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3477,10 +3488,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3488,34 +3499,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3525,7 +3536,7 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>82</v>
@@ -3540,13 +3551,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3564,34 +3575,34 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3599,10 +3610,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3625,19 +3636,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3662,13 +3673,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3686,7 +3697,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3698,7 +3709,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3710,10 +3721,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3721,21 +3732,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3744,22 +3755,22 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3769,7 +3780,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3784,13 +3795,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3808,45 +3819,45 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3857,7 +3868,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3869,13 +3880,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3926,13 +3937,13 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
@@ -3950,7 +3961,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3961,14 +3972,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3987,16 +3998,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4034,19 +4045,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4058,7 +4069,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4070,7 +4081,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4081,10 +4092,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4104,22 +4115,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4168,7 +4179,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4180,7 +4191,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4189,10 +4200,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4203,10 +4214,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4217,7 +4228,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4226,22 +4237,22 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4251,7 +4262,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4290,19 +4301,19 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4311,10 +4322,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4325,10 +4336,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4336,10 +4347,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4348,22 +4359,22 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4412,34 +4423,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4447,10 +4458,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4470,19 +4481,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4532,7 +4543,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4544,7 +4555,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4553,13 +4564,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4567,21 +4578,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4590,22 +4601,22 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4654,34 +4665,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4689,21 +4700,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4712,22 +4723,22 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4764,44 +4775,44 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4809,23 +4820,23 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4834,22 +4845,22 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4898,34 +4909,34 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4933,10 +4944,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4947,7 +4958,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4956,19 +4967,19 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5018,19 +5029,19 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5039,13 +5050,13 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5053,10 +5064,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5076,20 +5087,20 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5138,7 +5149,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5150,22 +5161,22 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5173,10 +5184,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5187,7 +5198,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5196,22 +5207,22 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5248,58 +5259,58 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
@@ -5309,7 +5320,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5318,22 +5329,22 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5358,11 +5369,11 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5380,45 +5391,45 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5429,7 +5440,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5441,13 +5452,13 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5498,13 +5509,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5522,7 +5533,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5533,14 +5544,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5559,16 +5570,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5606,19 +5617,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5630,7 +5641,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5642,7 +5653,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5653,10 +5664,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5676,22 +5687,22 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5740,7 +5751,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5752,7 +5763,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5761,10 +5772,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5775,10 +5786,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5789,7 +5800,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5798,22 +5809,22 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5823,7 +5834,7 @@
         <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>82</v>
@@ -5862,19 +5873,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5883,10 +5894,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5897,10 +5908,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5911,7 +5922,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5923,19 +5934,19 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5960,13 +5971,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -5984,19 +5995,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6005,10 +6016,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6019,14 +6030,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6045,19 +6056,19 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6082,13 +6093,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6106,7 +6117,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6118,33 +6129,33 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6158,7 +6169,7 @@
         <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6167,19 +6178,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6228,7 +6239,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6240,7 +6251,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6249,10 +6260,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6263,10 +6274,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6277,7 +6288,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6289,16 +6300,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6324,13 +6335,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6348,45 +6359,45 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6397,7 +6408,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6409,19 +6420,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6446,13 +6457,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6470,19 +6481,19 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6491,10 +6502,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6505,10 +6516,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6519,7 +6530,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6531,16 +6542,16 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6590,45 +6601,45 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6639,7 +6650,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6651,16 +6662,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6710,45 +6721,45 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6771,19 +6782,19 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6832,7 +6843,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6844,7 +6855,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6853,10 +6864,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6867,10 +6878,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6881,7 +6892,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6893,13 +6904,13 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6950,13 +6961,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -6974,7 +6985,7 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6985,14 +6996,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7011,16 +7022,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7070,7 +7081,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7082,7 +7093,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7094,7 +7105,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7105,14 +7116,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7125,25 +7136,25 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7192,7 +7203,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7204,7 +7215,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7216,7 +7227,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7227,10 +7238,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7241,7 +7252,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7253,13 +7264,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7310,19 +7321,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7331,10 +7342,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7345,10 +7356,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7359,7 +7370,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7371,13 +7382,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7428,31 +7439,31 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="AN46" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7463,10 +7474,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7477,7 +7488,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7489,19 +7500,19 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7526,13 +7537,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7550,31 +7561,31 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7585,10 +7596,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7611,19 +7622,19 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7648,13 +7659,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7672,7 +7683,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7684,19 +7695,19 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7707,10 +7718,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7721,7 +7732,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7733,17 +7744,17 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7792,19 +7803,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7816,7 +7827,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7827,10 +7838,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7841,7 +7852,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7853,13 +7864,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7910,19 +7921,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7931,10 +7942,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7945,10 +7956,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7968,19 +7979,19 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8030,7 +8041,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8042,7 +8053,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8051,10 +8062,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8065,10 +8076,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8088,19 +8099,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8150,7 +8161,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8162,7 +8173,7 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8171,10 +8182,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8185,10 +8196,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8208,22 +8219,22 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8272,7 +8283,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8284,7 +8295,7 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>468</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8293,10 +8304,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8307,10 +8318,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8321,7 +8332,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8333,13 +8344,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8390,13 +8401,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8414,7 +8425,7 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8425,14 +8436,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8451,16 +8462,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8510,7 +8521,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8522,7 +8533,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8534,7 +8545,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8545,14 +8556,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8565,25 +8576,25 @@
         <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8632,7 +8643,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8644,7 +8655,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8656,7 +8667,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8667,10 +8678,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8678,10 +8689,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8690,22 +8701,22 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8730,13 +8741,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8754,34 +8765,34 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8789,10 +8800,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8803,7 +8814,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -8812,22 +8823,22 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8876,45 +8887,45 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8925,7 +8936,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -8937,19 +8948,19 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -8974,13 +8985,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -8998,19 +9009,19 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9019,10 +9030,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9033,14 +9044,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9059,19 +9070,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9096,13 +9107,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9120,7 +9131,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9132,33 +9143,33 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9184,16 +9195,16 @@
         <v>83</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9242,7 +9253,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9254,7 +9265,7 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9263,10 +9274,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2379" uniqueCount="488">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,9 +293,6 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>clinical.diagnostics</t>
-  </si>
-  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -379,7 +376,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -437,10 +434,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -481,7 +474,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -561,7 +554,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -597,7 +590,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -703,6 +696,10 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -765,10 +762,6 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -796,7 +789,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -837,7 +830,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -895,7 +888,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -939,7 +932,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -992,7 +985,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1154,10 +1147,10 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>SNOMED CT Body site concepts</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1277,7 +1270,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1443,7 +1436,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1465,7 +1458,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1480,14 +1473,10 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1527,7 +1516,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2160,7 +2149,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2168,10 +2157,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2182,28 +2171,28 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2253,13 +2242,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2288,10 +2277,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2302,25 +2291,25 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2371,19 +2360,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2406,10 +2395,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2420,28 +2409,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2491,19 +2480,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2526,10 +2515,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2540,7 +2529,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2552,16 +2541,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2587,43 +2576,43 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2646,21 +2635,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2672,16 +2661,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2731,31 +2720,31 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2766,14 +2755,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2792,16 +2781,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2851,7 +2840,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2863,7 +2852,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2875,7 +2864,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2886,14 +2875,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2912,16 +2901,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2971,7 +2960,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2983,7 +2972,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2995,7 +2984,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3006,14 +2995,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3026,25 +3015,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3093,7 +3082,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3105,7 +3094,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3117,7 +3106,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3128,10 +3117,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3151,20 +3140,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3213,7 +3202,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3225,22 +3214,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3248,14 +3237,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3271,20 +3260,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3333,7 +3322,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3345,19 +3334,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3368,14 +3357,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3391,19 +3380,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3453,7 +3442,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3465,19 +3454,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3488,10 +3477,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3499,34 +3488,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="J14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3536,73 +3525,73 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="T14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3610,10 +3599,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3636,19 +3625,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3673,13 +3662,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3697,7 +3686,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3709,7 +3698,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3721,10 +3710,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3732,45 +3721,45 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3780,84 +3769,84 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK16" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AL16" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3868,7 +3857,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3880,13 +3869,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>95</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3937,31 +3926,31 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3972,14 +3961,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3998,16 +3987,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4045,19 +4034,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4069,7 +4058,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4081,7 +4070,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4092,10 +4081,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4115,22 +4104,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4179,7 +4168,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4191,7 +4180,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4200,10 +4189,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4214,10 +4203,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4228,31 +4217,31 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4262,70 +4251,70 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="T20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4336,10 +4325,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4347,34 +4336,34 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G21" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4423,34 +4412,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4458,10 +4447,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4481,19 +4470,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4543,7 +4532,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4555,7 +4544,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4564,13 +4553,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4578,45 +4567,45 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4665,34 +4654,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4700,45 +4689,45 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4775,44 +4764,44 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AF24" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4820,47 +4809,47 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4909,34 +4898,34 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4944,10 +4933,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4958,28 +4947,28 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5029,19 +5018,19 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5050,13 +5039,13 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5064,10 +5053,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5087,20 +5076,20 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5149,7 +5138,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5161,22 +5150,22 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5184,10 +5173,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5198,31 +5187,31 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K28" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5259,58 +5248,58 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
@@ -5320,31 +5309,31 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5369,11 +5358,11 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5391,45 +5380,45 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5440,7 +5429,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5452,13 +5441,13 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>95</v>
+        <v>217</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5509,31 +5498,31 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5544,14 +5533,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5570,16 +5559,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5617,19 +5606,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AC31" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AC31" t="s" s="2">
+      <c r="AD31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE31" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AD31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE31" t="s" s="2">
+      <c r="AF31" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5641,7 +5630,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5653,7 +5642,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5664,10 +5653,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5687,22 +5676,22 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5751,7 +5740,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5763,7 +5752,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5772,10 +5761,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5786,10 +5775,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5800,31 +5789,31 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K33" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5834,7 +5823,7 @@
         <v>82</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>82</v>
@@ -5873,31 +5862,31 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5908,10 +5897,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5922,7 +5911,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5934,19 +5923,19 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5971,55 +5960,55 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="Y34" t="s" s="2">
+      <c r="AA34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI34" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z34" t="s" s="2">
+      <c r="AJ34" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6030,14 +6019,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6056,19 +6045,19 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6093,13 +6082,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6117,7 +6106,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6129,33 +6118,33 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6169,7 +6158,7 @@
         <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6178,19 +6167,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6239,7 +6228,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6251,7 +6240,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6260,10 +6249,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6274,10 +6263,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6288,7 +6277,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6300,16 +6289,16 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6335,69 +6324,69 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AA37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>369</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6408,7 +6397,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6420,19 +6409,19 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6457,55 +6446,55 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="Z38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6516,10 +6505,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6530,7 +6519,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6542,16 +6531,16 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6601,45 +6590,45 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6650,7 +6639,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6662,16 +6651,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6721,45 +6710,45 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>396</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6782,19 +6771,19 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6843,7 +6832,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6855,19 +6844,19 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6878,10 +6867,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6892,7 +6881,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6904,13 +6893,13 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6961,31 +6950,31 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6996,14 +6985,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7022,16 +7011,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7081,7 +7070,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7093,7 +7082,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7105,7 +7094,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7116,14 +7105,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7136,25 +7125,25 @@
         <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7203,7 +7192,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7215,7 +7204,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7227,7 +7216,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7238,10 +7227,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7252,7 +7241,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7264,13 +7253,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7321,31 +7310,31 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7356,10 +7345,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7370,7 +7359,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7382,13 +7371,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7439,19 +7428,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7460,10 +7449,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7474,10 +7463,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7488,7 +7477,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7500,19 +7489,19 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7537,55 +7526,55 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="Z47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AA47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AN47" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7596,10 +7585,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7622,19 +7611,19 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7659,13 +7648,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7683,7 +7672,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7695,19 +7684,19 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7718,10 +7707,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7732,7 +7721,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7744,17 +7733,17 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7803,19 +7792,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7827,7 +7816,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7838,10 +7827,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7852,7 +7841,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7864,13 +7853,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7921,19 +7910,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7942,10 +7931,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7956,10 +7945,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7979,19 +7968,19 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8041,7 +8030,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8053,7 +8042,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8062,10 +8051,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8076,10 +8065,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8099,19 +8088,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8161,7 +8150,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8173,7 +8162,7 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8182,10 +8171,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8196,10 +8185,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8219,22 +8208,22 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8283,7 +8272,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8295,7 +8284,7 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>468</v>
+        <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8304,10 +8293,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8318,10 +8307,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8332,7 +8321,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8344,13 +8333,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8401,31 +8390,31 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8436,14 +8425,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8462,16 +8451,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8521,7 +8510,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8533,7 +8522,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8545,7 +8534,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8556,14 +8545,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8576,25 +8565,25 @@
         <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8643,7 +8632,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8655,7 +8644,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8667,7 +8656,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8678,10 +8667,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8689,34 +8678,34 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K57" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8741,14 +8730,14 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y57" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
       </c>
@@ -8765,34 +8754,34 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8800,10 +8789,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8814,31 +8803,31 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K58" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L58" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O58" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8887,45 +8876,45 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>482</v>
-      </c>
       <c r="AM58" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8936,7 +8925,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -8948,19 +8937,19 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -8985,55 +8974,55 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="AA59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI59" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="Z59" t="s" s="2">
+      <c r="AJ59" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9044,14 +9033,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9070,19 +9059,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9107,13 +9096,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9131,7 +9120,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9143,33 +9132,33 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9195,16 +9184,16 @@
         <v>83</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9253,7 +9242,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9265,7 +9254,7 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9274,10 +9263,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>

--- a/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
+++ b/branches/Richard/StructureDefinition-hiv-patient-pregnant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
